--- a/data/combat_table.xlsx
+++ b/data/combat_table.xlsx
@@ -210,17 +210,32 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>단일 캐릭터라 행은 1개(pc)뿐. 로더는 헤더(영문)=PlayerData 필드명으로 매핑한다.</t>
+        <t>단일 캐릭터라 행은 1개(pc). 헤더=PlayerData 필드명.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
-        <t>0~1 비율. 예) 0.9 = 충전 90% 이상이면 퍼펙트.</t>
+        <t>회피 연속 사용 횟수(스택). 부족하면 한 칸씩 차오름.</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AR1" authorId="0" shapeId="0">
       <text>
-        <t>잡몹/엘리트는 일섬 1방 즉사(데미지 무관). 이 값들은 보스 한정.</t>
+        <t>근접 기본 공격(부채꼴 스윙) 사거리.</t>
+      </text>
+    </comment>
+    <comment ref="AU1" authorId="0" shapeId="0">
+      <text>
+        <t>근접 스윙 데미지(잡몹 HP2→2면 한 방). 보스는 패리 없이 칩.</t>
+      </text>
+    </comment>
+    <comment ref="AV1" authorId="0" shapeId="0">
+      <text>
+        <t>스윙마다 카메라 흔들림 세기(매우 약하게).</t>
+      </text>
+    </comment>
+    <comment ref="AX1" authorId="0" shapeId="0">
+      <text>
+        <t>적 적중 시 게임이 잠깐 느려지는 배수(0~1). 작을수록 강한 히트스탑.</t>
       </text>
     </comment>
   </commentList>
@@ -236,46 +251,32 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>적 종류 코드 (ENUM)
-101 = melee  (근접몹)
-102 = ranged (원거리몹)
-103 = elite  (엘리트)
-201 = boss_1 (Ch1 보스)
-202 = boss_2 (Ch2 보스)
-203 = boss_3 (Ch3 보스)</t>
+101=melee/102=ranged/103=elite/104=leaper/201~203=boss</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>⚠ 로더 적용 규칙
-101~103 (잡몹/엘리트) = 참고용, 미적용
-  · 잡몹 HP: WaveManager 레벨업이 관리
-  · 엘리트 HP: effect_type 표(1=1/2=3/3=5/4=7)
-201~203 (보스) = 적용됨(변형 고정값)</t>
+        <t>⚠ 101~104=참고용, 201~203(보스)만 적용.</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>근접/엘리트/보스 = 부채 시작 거리. 원거리(102) = 사격 사거리.</t>
+        <t>화살 속도(유닛/초). 느릴수록 피하기 쉬움.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>원거리(102)는 여기에 aim_lock_duration 이 더해짐.</t>
+        <t>리프 발동 확률(104 전용).</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
-        <t>ENUM(bool): TRUE = WHITE(잡기, 데미지 ×2) 사용 / FALSE = 미사용</t>
+        <t>아머(경직 게이지). 0=한 방 잡몹, &gt;0=누적 데미지로 경직(엘리트4/보스6~8).</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
-        <t>ENUM(bool): TRUE = PURPLE(광역, 반경×1.5·각×1.3) / FALSE = 미사용</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
-      <text>
-        <t>ENUM(bool): TRUE = GREEN(다단, 후속 sweep) / FALSE = 미사용</t>
+        <t>아머 소거 시 경직(행동 불가) 시간(초).</t>
       </text>
     </comment>
   </commentList>
@@ -571,10 +572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="98" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,183 +591,42 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ 시트 구성</t>
+          <t>■ 시트: PC / ENEMY. 1행=영문 컬럼(로더 키), 2행=한글 설명, 3행~=데이터.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • PC    : 플레이어(거합 사무라이) 전투 파라미터 (1행=영문 컬럼, 2행=한글 설명, 3행=데이터)</t>
+          <t>■ ENUM/특수 컬럼 헤더에 마우스 올리면 코드표 메모.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • ENEMY : 잡몹/원거리/엘리트/보스(3변형) 전투 파라미터</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>■ CSV 연동: PC-&gt;data/pc.csv, ENEMY-&gt;data/enemy.csv. 빈 칸=기본값.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>■ 기본 공격=근접 부채꼴 스윙(LB)+카메라쉐이크+적중 히트스탑. SPACE=회피.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>■ 읽는 법</t>
+          <t>■ 아머(armor_max)=경직 게이지. 충돌: PC가 몬스터를 밀치며 통과(몬스터는 PC 못 밂).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 1행 = 정식 영어 컬럼명 (로더가 키로 사용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 2행 = 한글 설명 (사람용, 로더는 건너뜀)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 3행~ = 실제 데이터</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • ENUM/특수 컬럼 헤더에 마우스를 올리면 메모(코드표)가 뜬다. (예: ENEMY!id, enable_*_signal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>■ CSV 연동 (게임이 읽는 런타임 데이터)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • PC 시트  → data/pc.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • ENEMY 시트 → data/enemy.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 게임(scripts/managers/CombatData.gd)이 부팅 시 이 CSV 를 읽어 적용한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 워크플로우: 이 엑셀을 편집 → 각 시트를 같은 이름 CSV 로 내보내기(Save As CSV) → 게임 재실행.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (또는 data/*.csv 를 직접 편집해도 됨. 숫자 데이터는 인코딩 무관하게 읽힌다.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 값을 비우면 코드 기본값을 그대로 유지한다(안전).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>■ HP 적용 규칙 (중요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 잡몹(101)/엘리트(103) max_hp = 참고용, 로더 미적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (잡몹 HP=WaveManager 레벨업, 엘리트 HP=effect_type 표가 관리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 보스(201~203) max_hp = 적용됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>■ 엘리트 effect_type (스폰 시 지정, 표 컬럼 아님 / 참고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  101? 아니오 — effect_type ENUM: 1=폭발(HP1) / 2=보너스액션(HP3) / 3=불릿타임(HP5) / 4=실드(HP7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>■ 코드에 남은 값(표 미관리, 참고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 부채 텔레그래프 타이밍(잡몹 0.5/0.15, 보스 0.5/0.2), 화살 데미지(Arrow.gd=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 빌드(.exe)에서 읽으려면 export 필터에 *.csv 추가 필요(에디터 실행엔 무관)</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 적: 101 추적/102 원거리/103 엘리트/104 리프/201~203 보스</t>
         </is>
       </c>
     </row>
@@ -781,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -820,6 +680,21 @@
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="15" customWidth="1" min="35" max="35"/>
     <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="15" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="15" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="15" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1003,6 +878,81 @@
           <t>zen_burst_range_mult</t>
         </is>
       </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>evade_max_stacks</t>
+        </is>
+      </c>
+      <c r="AL1" s="5" t="inlineStr">
+        <is>
+          <t>evade_refill_time</t>
+        </is>
+      </c>
+      <c r="AM1" s="5" t="inlineStr">
+        <is>
+          <t>kunai_autoaim_damage</t>
+        </is>
+      </c>
+      <c r="AN1" s="5" t="inlineStr">
+        <is>
+          <t>kunai_autoaim_speed_mult</t>
+        </is>
+      </c>
+      <c r="AO1" s="5" t="inlineStr">
+        <is>
+          <t>kunai_move_spread_deg</t>
+        </is>
+      </c>
+      <c r="AP1" s="5" t="inlineStr">
+        <is>
+          <t>kunai_knockback</t>
+        </is>
+      </c>
+      <c r="AQ1" s="5" t="inlineStr">
+        <is>
+          <t>kunai_fire_move_mult</t>
+        </is>
+      </c>
+      <c r="AR1" s="5" t="inlineStr">
+        <is>
+          <t>melee_range</t>
+        </is>
+      </c>
+      <c r="AS1" s="5" t="inlineStr">
+        <is>
+          <t>melee_angle_deg</t>
+        </is>
+      </c>
+      <c r="AT1" s="5" t="inlineStr">
+        <is>
+          <t>melee_cooldown</t>
+        </is>
+      </c>
+      <c r="AU1" s="5" t="inlineStr">
+        <is>
+          <t>melee_damage</t>
+        </is>
+      </c>
+      <c r="AV1" s="5" t="inlineStr">
+        <is>
+          <t>melee_shake_amp</t>
+        </is>
+      </c>
+      <c r="AW1" s="5" t="inlineStr">
+        <is>
+          <t>melee_shake_dur</t>
+        </is>
+      </c>
+      <c r="AX1" s="5" t="inlineStr">
+        <is>
+          <t>melee_hitstop_scale</t>
+        </is>
+      </c>
+      <c r="AY1" s="5" t="inlineStr">
+        <is>
+          <t>melee_hitstop_dur</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1185,6 +1135,81 @@
           <t>젠버스트 사거리 배수(max_slash_range 대비)</t>
         </is>
       </c>
+      <c r="AK2" s="6" t="inlineStr">
+        <is>
+          <t>회피 스택 수(연속 대시 횟수)</t>
+        </is>
+      </c>
+      <c r="AL2" s="6" t="inlineStr">
+        <is>
+          <t>스택 전부 소진 후 가득 차기까지(초)</t>
+        </is>
+      </c>
+      <c r="AM2" s="6" t="inlineStr">
+        <is>
+          <t>자동락온(SPACE) 비도 데미지 — 한 방에 안 죽음</t>
+        </is>
+      </c>
+      <c r="AN2" s="6" t="inlineStr">
+        <is>
+          <t>자동락온 시 투사체 속도 배수(더 느림)</t>
+        </is>
+      </c>
+      <c r="AO2" s="6" t="inlineStr">
+        <is>
+          <t>이동 중 발사 탄도 분산(±도). 멈춰서 쏘면 0</t>
+        </is>
+      </c>
+      <c r="AP2" s="6" t="inlineStr">
+        <is>
+          <t>비도 피탄 시 적 밀림 속도(유닛/초, 스무스)</t>
+        </is>
+      </c>
+      <c r="AQ2" s="6" t="inlineStr">
+        <is>
+          <t>LB 사격/장전 중 이동속도 배수(0.5=50% 감속)</t>
+        </is>
+      </c>
+      <c r="AR2" s="6" t="inlineStr">
+        <is>
+          <t>근접 스윙 사거리(유닛)</t>
+        </is>
+      </c>
+      <c r="AS2" s="6" t="inlineStr">
+        <is>
+          <t>근접 부채꼴 각도(도, 커서 ±절반)</t>
+        </is>
+      </c>
+      <c r="AT2" s="6" t="inlineStr">
+        <is>
+          <t>근접 스윙 간격(초)=공격속도</t>
+        </is>
+      </c>
+      <c r="AU2" s="6" t="inlineStr">
+        <is>
+          <t>근접 스윙 데미지(잡몹 HP2→2면 한 방)</t>
+        </is>
+      </c>
+      <c r="AV2" s="6" t="inlineStr">
+        <is>
+          <t>스윙마다 카메라 흔들림 세기(유닛, 매우 약하게)</t>
+        </is>
+      </c>
+      <c r="AW2" s="6" t="inlineStr">
+        <is>
+          <t>스윙 카메라 흔들림 시간(초)</t>
+        </is>
+      </c>
+      <c r="AX2" s="6" t="inlineStr">
+        <is>
+          <t>적 적중 시 히트스탑 배수(0~1, 작을수록 강함)</t>
+        </is>
+      </c>
+      <c r="AY2" s="6" t="inlineStr">
+        <is>
+          <t>적 적중 시 히트스탑 시간(초)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1194,177 +1219,252 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD3" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE3" s="7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AF3" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AG3" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AH3" s="7" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AI3" s="7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AJ3" s="7" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AK3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" s="7" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="AM3" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN3" s="7" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="AO3" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AP3" s="7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ3" s="7" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="R3" s="7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="V3" s="7" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="W3" s="7" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="X3" s="7" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="Y3" s="7" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="Z3" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA3" s="7" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="AB3" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC3" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD3" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE3" s="7" t="inlineStr">
+      <c r="AR3" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AS3" s="7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AF3" s="7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AG3" s="7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AH3" s="7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI3" s="7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AJ3" s="7" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="AT3" s="7" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AU3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV3" s="7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AW3" s="7" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AX3" s="7" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AY3" s="7" t="inlineStr">
+        <is>
+          <t>0.045</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1409,6 +1509,11 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1542,6 +1647,31 @@
           <t>green_ratio</t>
         </is>
       </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>leap_chance</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>leap_radius</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>leap_damage</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>armor_max</t>
+        </is>
+      </c>
+      <c r="AE1" s="5" t="inlineStr">
+        <is>
+          <t>stagger_duration</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1674,6 +1804,31 @@
           <t>GREEN 확률(0~1)</t>
         </is>
       </c>
+      <c r="AA2" s="6" t="inlineStr">
+        <is>
+          <t>리프(내려찍기) 발동 확률(0~1, 근접 전용)</t>
+        </is>
+      </c>
+      <c r="AB2" s="6" t="inlineStr">
+        <is>
+          <t>리프 슬램 원형 반경(유닛)</t>
+        </is>
+      </c>
+      <c r="AC2" s="6" t="inlineStr">
+        <is>
+          <t>리프 슬램 데미지</t>
+        </is>
+      </c>
+      <c r="AD2" s="6" t="inlineStr">
+        <is>
+          <t>아머(경직 게이지) 최대치 — 0=아머 없음(한 방 처치 잡몹). 데미지 누적 0이면 경직.</t>
+        </is>
+      </c>
+      <c r="AE2" s="6" t="inlineStr">
+        <is>
+          <t>아머 소거 시 경직(행동 불가) 시간(초).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1688,7 +1843,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1703,7 +1858,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -1721,8 +1876,16 @@
           <t>70</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr"/>
-      <c r="K3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
       <c r="L3" s="7" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
       <c r="N3" s="7" t="inlineStr"/>
@@ -1738,6 +1901,23 @@
       <c r="X3" s="7" t="inlineStr"/>
       <c r="Y3" s="7" t="inlineStr"/>
       <c r="Z3" s="7" t="inlineStr"/>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr"/>
+      <c r="AC3" s="7" t="inlineStr"/>
+      <c r="AD3" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" s="7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1752,7 +1932,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1767,7 +1947,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr"/>
@@ -1782,12 +1962,12 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr"/>
@@ -1802,6 +1982,19 @@
       <c r="X4" s="7" t="inlineStr"/>
       <c r="Y4" s="7" t="inlineStr"/>
       <c r="Z4" s="7" t="inlineStr"/>
+      <c r="AA4" s="7" t="inlineStr"/>
+      <c r="AB4" s="7" t="inlineStr"/>
+      <c r="AC4" s="7" t="inlineStr"/>
+      <c r="AD4" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" s="7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1816,7 +2009,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -1827,7 +2020,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1870,6 +2063,19 @@
       <c r="X5" s="7" t="inlineStr"/>
       <c r="Y5" s="7" t="inlineStr"/>
       <c r="Z5" s="7" t="inlineStr"/>
+      <c r="AA5" s="7" t="inlineStr"/>
+      <c r="AB5" s="7" t="inlineStr"/>
+      <c r="AC5" s="7" t="inlineStr"/>
+      <c r="AD5" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE5" s="7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1884,7 +2090,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1899,7 +2105,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1982,6 +2188,19 @@
           <t>0</t>
         </is>
       </c>
+      <c r="AA6" s="7" t="inlineStr"/>
+      <c r="AB6" s="7" t="inlineStr"/>
+      <c r="AC6" s="7" t="inlineStr"/>
+      <c r="AD6" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE6" s="7" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1996,7 +2215,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2011,7 +2230,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2094,6 +2313,19 @@
           <t>0</t>
         </is>
       </c>
+      <c r="AA7" s="7" t="inlineStr"/>
+      <c r="AB7" s="7" t="inlineStr"/>
+      <c r="AC7" s="7" t="inlineStr"/>
+      <c r="AD7" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE7" s="7" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2108,7 +2340,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2123,7 +2355,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2206,6 +2438,100 @@
           <t>0.1</t>
         </is>
       </c>
+      <c r="AA8" s="7" t="inlineStr"/>
+      <c r="AB8" s="7" t="inlineStr"/>
+      <c r="AC8" s="7" t="inlineStr"/>
+      <c r="AD8" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE8" s="7" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>leaper</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="7" t="inlineStr"/>
+      <c r="V9" s="7" t="inlineStr"/>
+      <c r="W9" s="7" t="inlineStr"/>
+      <c r="X9" s="7" t="inlineStr"/>
+      <c r="Y9" s="7" t="inlineStr"/>
+      <c r="Z9" s="7" t="inlineStr"/>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AC9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD9" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" s="7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
